--- a/Insiders/History/History.xlsx
+++ b/Insiders/History/History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,264 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>19.77s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21:03:23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Food &amp; Dining</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Chīrāla, Andhra Pradesh, IN</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20.11s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>21:03:23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Food &amp; Dining</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Chīrāla, Andhra Pradesh, IN</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20.11s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21:03:53</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Makemytrip</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Chīrāla, Andhra Pradesh, IN</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>49.96s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>21:19:27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>temple</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Food &amp; Dining</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chīrāla, Andhra Pradesh, IN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18.36s</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22:04:26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Food &amp; Dining</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vijayawada, Andhra Pradesh, IN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22:12:36</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Food &amp; Dining</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vijayawada, Andhra Pradesh, IN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1m 2.11s</t>
         </is>
       </c>
     </row>
